--- a/output/pl1takdl.xlsx
+++ b/output/pl1takdl.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Назва</t>
   </si>
@@ -83,6 +83,12 @@
   </si>
   <si>
     <t>Кубок Трішки Несередзем'я-2025</t>
+  </si>
+  <si>
+    <t>Бузький Гард-9</t>
+  </si>
+  <si>
+    <t>Борисфен 11: Ірклій</t>
   </si>
 </sst>
 </file>
@@ -440,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -619,6 +625,22 @@
         <v>5.9</v>
       </c>
     </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>4.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/pl1takdl.xlsx
+++ b/output/pl1takdl.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Назва</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t>Борисфен 11: Ірклій</t>
+  </si>
+  <si>
+    <t>Справжній детектив-3</t>
+  </si>
+  <si>
+    <t>Борисфен 12: Верхня Хортиця</t>
   </si>
 </sst>
 </file>
@@ -446,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -641,6 +647,22 @@
         <v>4.14</v>
       </c>
     </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>6.23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>3.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/pl1takdl.xlsx
+++ b/output/pl1takdl.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Назва</t>
   </si>
@@ -95,6 +95,12 @@
   </si>
   <si>
     <t>Борисфен 12: Верхня Хортиця</t>
+  </si>
+  <si>
+    <t>Поки зорить Чумацький Шлях 2</t>
+  </si>
+  <si>
+    <t>Синхрон ЛУК 25/26. Зима</t>
   </si>
 </sst>
 </file>
@@ -452,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -663,6 +669,22 @@
         <v>3.46</v>
       </c>
     </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>3.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
